--- a/Hardware/EET_BMS_Layout/bom/BOM_EET-BMS.xlsx
+++ b/Hardware/EET_BMS_Layout/bom/BOM_EET-BMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavel\Nextcloud\Arbeit\Projekte\STM32_Projekte\Open_BMS\Open_BMS\Hardware\EET_BMS_Layout\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A9BA8A-C378-4F84-BEA5-611FFE293E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6AF8AF-71C0-4D95-8D5F-105046B73F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="132">
   <si>
     <t>Designator</t>
   </si>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>JLCPCB</t>
+  </si>
+  <si>
+    <t>Composite</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/</t>
   </si>
 </sst>
 </file>
@@ -539,14 +545,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
@@ -882,1133 +885,1142 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="11" t="s">
+      <c r="D2" s="8">
+        <v>1.206</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="9">
+        <f t="shared" ref="F2:F39" si="0">C2*D2</f>
+        <v>1.206</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="4"/>
+      <c r="H2" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="37.299999999999997" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>38</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="10">
-        <f t="shared" ref="F3:F39" si="0">C3*D3</f>
+      <c r="E3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9">
+        <f t="shared" si="0"/>
         <v>2.1280000000000001</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="G3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="24.9" x14ac:dyDescent="0.4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>14</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="10">
+      <c r="E4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="9">
         <f t="shared" si="0"/>
         <v>0.44800000000000001</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="G4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>8</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="E5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="9">
         <f t="shared" si="0"/>
         <v>0.63200000000000001</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="G5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>6</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>2.3E-2</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9">
         <f t="shared" si="0"/>
         <v>0.13800000000000001</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="G6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>4</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="9">
         <f t="shared" si="0"/>
         <v>0.36799999999999999</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="G7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>3</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>0.154</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="E8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="9">
         <f t="shared" si="0"/>
         <v>0.46199999999999997</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="5" t="s">
+      <c r="G8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>2</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="E9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="9">
         <f t="shared" si="0"/>
         <v>0.152</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="G9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>2</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>0.124</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="E10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="9">
         <f t="shared" si="0"/>
         <v>0.248</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="G10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>2</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="E11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="9">
         <f t="shared" si="0"/>
         <v>0.13400000000000001</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="G11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="24.9" x14ac:dyDescent="0.4">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>13</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>2.4E-2</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="E12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="9">
         <f t="shared" si="0"/>
         <v>0.312</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="5" t="s">
+      <c r="G12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>7</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="E13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="9">
         <f t="shared" si="0"/>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="G13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>6</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="10">
+      <c r="E14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="9">
         <f t="shared" si="0"/>
         <v>5.3999999999999992E-2</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="5" t="s">
+      <c r="G14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>5</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>2.7E-2</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="10">
+      <c r="E15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="9">
         <f t="shared" si="0"/>
         <v>0.13500000000000001</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="5" t="s">
+      <c r="G15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>5</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>1.4E-2</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="10">
+      <c r="E16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="9">
         <f t="shared" si="0"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="5" t="s">
+      <c r="G16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>5</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>1.44E-2</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="10">
+      <c r="E17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="9">
         <f t="shared" si="0"/>
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="5" t="s">
+      <c r="G17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>3</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>1.44E-2</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="10">
+      <c r="E18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="9">
         <f t="shared" si="0"/>
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" s="5" t="s">
+      <c r="G18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>2</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <v>0.16</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="10">
+      <c r="E19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="9">
         <f t="shared" si="0"/>
         <v>0.32</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" s="5" t="s">
+      <c r="G19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>1</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>0.08</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="E20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="9">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I20" s="5" t="s">
+      <c r="G20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>1</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>0.12</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="10">
+      <c r="E21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="9">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
-      <c r="G21" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I21" s="5" t="s">
+      <c r="G21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="7">
         <v>4</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="10">
+      <c r="E22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="9">
         <f t="shared" si="0"/>
         <v>0.34399999999999997</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I22" s="5" t="s">
+      <c r="G22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>1</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <v>0.08</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="10">
+      <c r="E23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="9">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I23" s="5" t="s">
+      <c r="G23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="7">
         <v>2</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>1.0269999999999999</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="10">
+      <c r="E24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="9">
         <f t="shared" si="0"/>
         <v>2.0539999999999998</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I24" s="5" t="s">
+      <c r="G24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="7">
         <v>1</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="8">
         <v>7.14</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="9">
         <f t="shared" si="0"/>
         <v>7.14</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I25" s="5" t="s">
+      <c r="H25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="7">
         <v>1</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <v>3.9</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="10">
+      <c r="E26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="9">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I26" s="5" t="s">
+      <c r="G26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>1</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <v>0.84</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="10">
+      <c r="E27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="9">
         <f t="shared" si="0"/>
         <v>0.84</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I27" s="5" t="s">
+      <c r="G27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="7">
         <v>1</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>20.04</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="9">
         <f t="shared" si="0"/>
         <v>20.04</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I28" s="5" t="s">
+      <c r="H28" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="4" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="7">
         <v>1</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>1.82</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="10">
+      <c r="E29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="9">
         <f t="shared" si="0"/>
         <v>1.82</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I29" s="5" t="s">
+      <c r="H29" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="4" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="7">
         <v>1</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="8">
         <v>0.40600000000000003</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="10">
+      <c r="E30" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="9">
         <f t="shared" si="0"/>
         <v>0.40600000000000003</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" s="5" t="s">
+      <c r="G30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <v>2</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="8">
         <v>1.0349999999999999</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="10">
+      <c r="E31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="9">
         <f t="shared" si="0"/>
         <v>2.0699999999999998</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="5" t="s">
+      <c r="G31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="7">
         <v>1</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>1.64</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="10">
+      <c r="E32" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="9">
         <f t="shared" si="0"/>
         <v>1.64</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I32" s="5" t="s">
+      <c r="G32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <v>1</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="8">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="10">
+      <c r="E33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="9">
         <f t="shared" si="0"/>
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I33" s="5" t="s">
+      <c r="G33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="7">
         <v>4</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="8">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="10">
+      <c r="E34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="9">
         <f t="shared" si="0"/>
         <v>0.316</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" s="5" t="s">
+      <c r="G34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="7">
         <v>1</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="8">
         <v>0.157</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="10">
+      <c r="E35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="9">
         <f t="shared" si="0"/>
         <v>0.157</v>
       </c>
-      <c r="G35" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I35" s="5" t="s">
+      <c r="G35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="7">
         <v>1</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="10">
+      <c r="E36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="9">
         <f t="shared" si="0"/>
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="G36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I36" s="5" t="s">
+      <c r="G36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="7">
         <v>2</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>0.114</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="10">
+      <c r="E37" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="9">
         <f t="shared" si="0"/>
         <v>0.22800000000000001</v>
       </c>
-      <c r="G37" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I37" s="5" t="s">
+      <c r="G37" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I37" s="4" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="7">
         <v>2</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>0.29899999999999999</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="10">
+      <c r="E38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="9">
         <f t="shared" si="0"/>
         <v>0.59799999999999998</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I38" s="5" t="s">
+      <c r="G38" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="7">
         <v>1</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="8">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="10">
+      <c r="E39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="9">
         <f t="shared" si="0"/>
         <v>0.39200000000000002</v>
       </c>
-      <c r="G39" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I39" s="5" t="s">
+      <c r="G39" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>127</v>
       </c>
     </row>
